--- a/documents/Customer upload.xlsx
+++ b/documents/Customer upload.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darryllrobinson/Documents/projects/ciab/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6755A22-5D4E-BC40-A932-46E7BA4E2A93}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A2A58D-778E-674A-A056-4D0CB301E658}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28380" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="28120" windowHeight="15160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Customers" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Customers!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Customers!$A$1:$J$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,11 +36,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="170">
   <si>
     <t>3RD101</t>
   </si>
   <si>
+    <t>5OH012</t>
+  </si>
+  <si>
     <t>AEO101</t>
   </si>
   <si>
@@ -50,6 +53,12 @@
     <t>ALJ101</t>
   </si>
   <si>
+    <t>ATT102</t>
+  </si>
+  <si>
+    <t>BAC101</t>
+  </si>
+  <si>
     <t>BBQ101</t>
   </si>
   <si>
@@ -62,6 +71,9 @@
     <t>CEN102</t>
   </si>
   <si>
+    <t>CH0243</t>
+  </si>
+  <si>
     <t>CJS101</t>
   </si>
   <si>
@@ -77,9 +89,21 @@
     <t>DOR101</t>
   </si>
   <si>
+    <t>DV1144</t>
+  </si>
+  <si>
     <t>GAT101</t>
   </si>
   <si>
+    <t>GRA078</t>
+  </si>
+  <si>
+    <t>GRA297</t>
+  </si>
+  <si>
+    <t>GRA586</t>
+  </si>
+  <si>
     <t>GRO101</t>
   </si>
   <si>
@@ -98,12 +122,24 @@
     <t>JAB101</t>
   </si>
   <si>
+    <t>LBV001</t>
+  </si>
+  <si>
+    <t>MCC104</t>
+  </si>
+  <si>
     <t>MLS101</t>
   </si>
   <si>
     <t>MON101</t>
   </si>
   <si>
+    <t>MOS103</t>
+  </si>
+  <si>
+    <t>MYE046</t>
+  </si>
+  <si>
     <t>NEP101</t>
   </si>
   <si>
@@ -113,6 +149,9 @@
     <t>ONE201</t>
   </si>
   <si>
+    <t>PAM101</t>
+  </si>
+  <si>
     <t>PAT101</t>
   </si>
   <si>
@@ -125,9 +164,27 @@
     <t>SAI102</t>
   </si>
   <si>
+    <t>SIB210</t>
+  </si>
+  <si>
+    <t>SLI035</t>
+  </si>
+  <si>
     <t>SUP104</t>
   </si>
   <si>
+    <t>TLA141</t>
+  </si>
+  <si>
+    <t>TW0113</t>
+  </si>
+  <si>
+    <t>TW0247</t>
+  </si>
+  <si>
+    <t>TWA292</t>
+  </si>
+  <si>
     <t>AEONOVA 360</t>
   </si>
   <si>
@@ -140,18 +197,33 @@
     <t>BONTIWORX (PTY) LTD</t>
   </si>
   <si>
+    <t>BRONWYN BOTHA</t>
+  </si>
+  <si>
+    <t>CANDICE ZAAIMAN</t>
+  </si>
+  <si>
     <t>CAPRICORN INVESTMENT GROUP (PTY) LTD</t>
   </si>
   <si>
     <t>CENTRAL PARK</t>
   </si>
   <si>
+    <t>CHERISE ANSARA</t>
+  </si>
+  <si>
     <t>COOL IDEAS SERVICE PROVIDER</t>
   </si>
   <si>
     <t>DORON DIAMONDS</t>
   </si>
   <si>
+    <t>DR PUCKS/COMOLINA</t>
+  </si>
+  <si>
+    <t>FARREN PRETORIUS</t>
+  </si>
+  <si>
     <t>HUAMIN TRADING</t>
   </si>
   <si>
@@ -167,30 +239,69 @@
     <t>JAB DRIED FRUIT PRODUCTS (PTY) LTD</t>
   </si>
   <si>
+    <t>JUERGEN SCHREIBER</t>
+  </si>
+  <si>
+    <t>JUSTIN MCCALLUM</t>
+  </si>
+  <si>
+    <t>KATE MODIMA BODIBA</t>
+  </si>
+  <si>
+    <t>KIMENGWA NGAMBI</t>
+  </si>
+  <si>
+    <t>LUKE JOHN BACKOS</t>
+  </si>
+  <si>
+    <t>LYNETTE WATSON</t>
+  </si>
+  <si>
     <t>MATTER INVESTMENTS (PTY) LTD</t>
   </si>
   <si>
+    <t>MATTHEW PEARCE</t>
+  </si>
+  <si>
     <t>MDF MANAGEMENT HOLDINGS (PTY) LTD</t>
   </si>
   <si>
+    <t>MUTSI PHAKISO MOSOEU</t>
+  </si>
+  <si>
     <t>N GATTOO INC T/A GATTOO ATTORNEYS</t>
   </si>
   <si>
     <t>NEPIC (PTY) LTD</t>
   </si>
   <si>
+    <t>NIKALYE OLDJOHN</t>
+  </si>
+  <si>
     <t>NKANYISO ICT (See Bureau report for Bukosini)</t>
   </si>
   <si>
+    <t>ODIEGWU TIMOTHY EKENE</t>
+  </si>
+  <si>
     <t>ONELOGIX VDS</t>
   </si>
   <si>
+    <t>OSENI SAMUEL</t>
+  </si>
+  <si>
     <t>PATACHOU PATISSERIE (PTY) LTD</t>
   </si>
   <si>
+    <t>PAUL USIRI</t>
+  </si>
+  <si>
     <t>PROPERTY HELPLINE (PTY) LTD</t>
   </si>
   <si>
+    <t>RAJI MOSHOOD KOLAWOLE</t>
+  </si>
+  <si>
     <t>REVIEWKING (PTY) LTD</t>
   </si>
   <si>
@@ -203,9 +314,15 @@
     <t>SUPERSPORT INTERNATIONAL</t>
   </si>
   <si>
+    <t>TANIA DU PLESSIS</t>
+  </si>
+  <si>
     <t>ILK101</t>
   </si>
   <si>
+    <t>Enterprise</t>
+  </si>
+  <si>
     <t>Business client</t>
   </si>
   <si>
@@ -227,6 +344,9 @@
     <t>2013/103761/07</t>
   </si>
   <si>
+    <t>P7</t>
+  </si>
+  <si>
     <t>2016/402942/07</t>
   </si>
   <si>
@@ -236,6 +356,12 @@
     <t>2015/032922/07</t>
   </si>
   <si>
+    <t>Consumer</t>
+  </si>
+  <si>
+    <t>Fibre Fast Uncapped 20Mbps @ R949</t>
+  </si>
+  <si>
     <t>2016/076408/07</t>
   </si>
   <si>
@@ -245,6 +371,12 @@
     <t>Once Installation</t>
   </si>
   <si>
+    <t>Home Client</t>
+  </si>
+  <si>
+    <t>DO</t>
+  </si>
+  <si>
     <t>ISP</t>
   </si>
   <si>
@@ -260,6 +392,9 @@
     <t>FTTB</t>
   </si>
   <si>
+    <t>FTTH</t>
+  </si>
+  <si>
     <t>2011/113336/07</t>
   </si>
   <si>
@@ -281,12 +416,21 @@
     <t>Final Liquidation</t>
   </si>
   <si>
+    <t>ZN436027</t>
+  </si>
+  <si>
     <t>2006/006974/07</t>
   </si>
   <si>
     <t>Fibre Paced Business Uncapped 20Mb</t>
   </si>
   <si>
+    <t>Zero Rated</t>
+  </si>
+  <si>
+    <t>Fibre Fast Uncapped 50Mbps @ R1099</t>
+  </si>
+  <si>
     <t>2015/347727/07</t>
   </si>
   <si>
@@ -296,6 +440,9 @@
     <t>2010/006836/07</t>
   </si>
   <si>
+    <t>Fibre Fast Uncapped 100Mbps @ R1599</t>
+  </si>
+  <si>
     <t>2009/019143/21</t>
   </si>
   <si>
@@ -305,21 +452,33 @@
     <t>2014/024218/07</t>
   </si>
   <si>
+    <t>Fibre Fast Uncapped 10Mbps @ R699699</t>
+  </si>
+  <si>
     <t>2015232312/07</t>
   </si>
   <si>
+    <t>A05644330</t>
+  </si>
+  <si>
     <t>Voluntary Liquidation</t>
   </si>
   <si>
     <t>2015/198200/07</t>
   </si>
   <si>
+    <t>CN411465</t>
+  </si>
+  <si>
     <t>2015/097337/07</t>
   </si>
   <si>
     <t>2002/002514/07</t>
   </si>
   <si>
+    <t>A037258703</t>
+  </si>
+  <si>
     <t>2016/179836/07</t>
   </si>
   <si>
@@ -335,9 +494,27 @@
     <t>2015/137696/07</t>
   </si>
   <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>CompanyRegNo</t>
+  </si>
+  <si>
     <t>BAKGATLA BA KGAFELA INVESTMENT HOLDINGS (BBKIH)</t>
   </si>
   <si>
+    <t>ConsumerIDNumber</t>
+  </si>
+  <si>
+    <t>CIPCStatus</t>
+  </si>
+  <si>
+    <t>Customer_Type</t>
+  </si>
+  <si>
+    <t>ProductType</t>
+  </si>
+  <si>
     <t>CRAZY JELLY STORE (PTY) LTD</t>
   </si>
   <si>
@@ -356,28 +533,19 @@
     <t>SIMPLYFAI</t>
   </si>
   <si>
+    <t>OperatorShortCode</t>
+  </si>
+  <si>
     <t>SADV</t>
   </si>
   <si>
-    <t>customerRefNo</t>
-  </si>
-  <si>
-    <t>companyName</t>
-  </si>
-  <si>
-    <t>customerType</t>
-  </si>
-  <si>
-    <t>operatorShortCode</t>
-  </si>
-  <si>
-    <t>regNumber</t>
-  </si>
-  <si>
-    <t>productType</t>
-  </si>
-  <si>
-    <t>cipcStatus</t>
+    <t>CustomerEntity</t>
+  </si>
+  <si>
+    <t>IDVStatus</t>
+  </si>
+  <si>
+    <t>CustomerNumber</t>
   </si>
 </sst>
 </file>
@@ -731,603 +899,1088 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB48243-9E74-4A3C-B555-A218E7D8E966}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="1"/>
+    <col min="4" max="4" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="14">
+        <v>167</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="14">
       <c r="A2" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>94</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="14">
+        <v>67</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>94</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="14">
       <c r="A5" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>94</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="14">
+        <v>94</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>106</v>
+      </c>
+      <c r="F7" s="2">
+        <v>7009090150081</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>67</v>
+        <v>106</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
+        <v>8302015147087</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>111</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="14">
+        <v>103</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="14">
       <c r="A10" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="14">
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>108</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>95</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>71</v>
+        <v>106</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2">
+        <v>7512050161089</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>72</v>
+        <v>159</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>114</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" ht="14">
       <c r="A15" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>89</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>113</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>160</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="14">
       <c r="A18" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="28">
+        <v>94</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="F19" s="2">
+        <v>8407180192089</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="1" t="s">
+      <c r="D20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="14">
-      <c r="A21" s="1" t="s">
+      <c r="G21" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1" t="s">
+      <c r="F22" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>56</v>
+      <c r="F23" s="2">
+        <v>8811190948085</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>94</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>94</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>63</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="28">
       <c r="A27" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:7">
+        <v>64</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>94</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="14">
       <c r="A29" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>94</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>99</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>94</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>106</v>
+      </c>
+      <c r="F31" s="2">
+        <v>8903290108080</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>56</v>
+        <v>68</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="2">
+        <v>8102035303086</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="14">
+      <c r="A34" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" s="2">
+        <v>8812185359080</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" s="2">
+        <v>8909290302086</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2">
+        <v>7906200036086</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2">
+        <v>9305031189081</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G32">
-    <sortCondition ref="B2:B32"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:J51">
+    <sortCondition ref="B2:B51"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
